--- a/www/download/COUNTRY.MLT.rpA2.xlsx
+++ b/www/download/COUNTRY.MLT.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>Malta</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.821684755536959</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.839100636076563</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.898078280441284</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.904384898541739</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.929851826238597</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.01871863654664</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.04756224641374</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1.00792264839678</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.877192137997102</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.802021683764487</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.804162377075274</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>0.793408381912368</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.724495030641948</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.679660773115357</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>0.716576242819136</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>3.45282875801165</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.139</t>
+          <t>2.98114822813642</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>3.84327080989702</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>3.45665342501616</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>2.83743237454545</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>2.56124784470886</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>1.63141056773142</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>1.86915791169404</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>2.15319170535724</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>2.33487517590884</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>2.13679353342383</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.154</t>
+          <t>2.2430812771869</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.159</t>
+          <t>2.00431309726332</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>1.90422847960078</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.162</t>
+          <t>2.1724646894295</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.122</t>
+          <t>2.05200709475523</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>1.82106674962404</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.123</t>
+          <t>2.4387554511913</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>2.15815056193225</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.127</t>
+          <t>1.72769187525385</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.128</t>
+          <t>1.53979866809314</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>0.896699907379644</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.134</t>
+          <t>1.08946098857587</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>1.41487585723537</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0.131</t>
+          <t>1.33626814712358</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>1.30557022241172</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>1.40281934718043</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>1.28743577490761</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>1.15063524042548</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>1.41196129066721</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>272.138</t>
+          <t>0.577939169865004</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>273.341</t>
+          <t>0.47766742358755</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>274.43</t>
+          <t>0.815590350271405</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>278.239</t>
+          <t>0.655970492694631</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>282.002</t>
+          <t>0.463424265835948</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>285.185</t>
+          <t>0.378224943319527</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>244.532</t>
+          <t>0.0408040467285971</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>288.899</t>
+          <t>0.141972028987236</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>277.161</t>
+          <t>-0.158355026283344</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>0.287203983534347</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>286.041</t>
+          <t>0.284606196767848</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>287.987</t>
+          <t>0.312784264269679</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>300.123</t>
+          <t>0.245513636979112</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>306.883</t>
+          <t>0.0763804840890974</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>307.78</t>
+          <t>0.230451548757841</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>239.98</t>
+          <t>589625657.536323</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>241.04</t>
+          <t>589120157.175958</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>242.001</t>
+          <t>500997603.092928</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>245.359</t>
+          <t>537497096.484977</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>248.678</t>
+          <t>619498452.973686</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>251.485</t>
+          <t>715911158.777118</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>216.96</t>
+          <t>585596397.57851</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>256.499</t>
+          <t>608029558.856201</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>245.286</t>
+          <t>639941872.813791</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>250.577</t>
+          <t>624592275.871377</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>252.301</t>
+          <t>594730638.488169</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>253.898</t>
+          <t>666829747.996617</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>264.56</t>
+          <t>666827406.686292</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>271.437</t>
+          <t>697156450.241556</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>264.649</t>
+          <t>620933246.188267</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>15.32</t>
+          <t>180198571.08385</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>15.16</t>
+          <t>195939719.215439</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>14.14</t>
+          <t>158907602.296784</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>13.11</t>
+          <t>174187214.974393</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>13.5</t>
+          <t>202474739.163574</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>13.76</t>
+          <t>219113975.272536</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>13.46</t>
+          <t>252779784.659229</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>273036753.120331</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>307241422.498978</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>17.18</t>
+          <t>245760972.033497</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>18.13</t>
+          <t>253074881.94159</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>18.46</t>
+          <t>249916143.512192</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>276343220.713324</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>20.79</t>
+          <t>314507812.828019</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>21.2</t>
+          <t>277090501.84865</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>3406980.18758809</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>3348310.59971034</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16.87</t>
+          <t>2995589.39669276</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>16.02</t>
+          <t>2966971.88158328</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>17.47</t>
+          <t>3277993.75794695</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>17.99</t>
+          <t>3520358.70511287</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>18.7</t>
+          <t>3157772.73017163</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>3071288.07588457</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>13.32</t>
+          <t>2716903.85594805</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>19.53</t>
+          <t>2458517.59167052</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>19.74</t>
+          <t>2161433.03238353</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>20.78</t>
+          <t>2418256.84132921</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>19.9</t>
+          <t>2018073.55550392</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>19.75</t>
+          <t>1864476.58469023</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>21.68</t>
+          <t>1965864.05979458</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>67.69</t>
+          <t>1086.98154363151</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>67.16</t>
+          <t>1080.76869271216</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>68.99</t>
+          <t>1034.45447571861</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>70.87</t>
+          <t>1004.1665543423</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>69.03</t>
+          <t>1055.1095364361</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>68.25</t>
+          <t>1079.94516849042</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>67.83</t>
+          <t>908.700876220005</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>67.5</t>
+          <t>1080.43287771508</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>74.3</t>
+          <t>1129.43127081794</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>63.28</t>
+          <t>1317.81498129741</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>62.12</t>
+          <t>1371.37399304459</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>60.76</t>
+          <t>1444.25154756081</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>60.99</t>
+          <t>1609.36120258134</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>59.46</t>
+          <t>1746.04852233074</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>57.12</t>
+          <t>1649.94698906739</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>23.32</t>
+          <t>2572.03516598435</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>23.25</t>
+          <t>2561.98234325186</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22.02</t>
+          <t>2142.83520834723</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>20.82</t>
+          <t>2270.61256770174</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>21.14</t>
+          <t>2700.08400607167</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>21.54</t>
+          <t>3138.09736214988</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>21.58</t>
+          <t>2476.15702176446</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>22.38</t>
+          <t>2604.06633454643</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>2934.39853458804</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>26.64</t>
+          <t>3106.31788743071</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>27.95</t>
+          <t>3146.11159753236</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>28.64</t>
+          <t>3671.38830705246</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>29.8</t>
+          <t>4115.74527258751</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>4700.53191300226</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>32.93</t>
+          <t>3869.68750097756</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>22.31</t>
+          <t>1.4475150159286</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>23.08</t>
+          <t>1.27148460522877</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>1.73028390593478</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>1.45103926657973</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>1.16343766155602</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>23.62</t>
+          <t>1.03653091717413</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>24.37</t>
+          <t>0.536247890203575</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>24.07</t>
+          <t>0.689374537161907</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>23.58</t>
+          <t>0.515599788972781</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>1.03344511803101</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>24.65</t>
+          <t>1.00057622623835</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>25.54</t>
+          <t>1.08611372206193</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>24.79</t>
+          <t>0.967758665477225</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>24.48</t>
+          <t>0.801206708620414</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>26.14</t>
+          <t>1.07426239407753</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>54.37</t>
+          <t>935.033766716748</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>53.67</t>
+          <t>962.436088886035</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>55.75</t>
+          <t>878.112097574302</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>57.86</t>
+          <t>988.361789538299</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>55.8</t>
+          <t>1028.45972006696</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>54.84</t>
+          <t>1079.4579623307</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>54.05</t>
+          <t>862.927322251072</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>53.56</t>
+          <t>857.643554506389</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>50.27</t>
+          <t>1092.12927592513</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>48.72</t>
+          <t>1192.83169298121</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>47.41</t>
+          <t>1235.83258064407</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>45.82</t>
+          <t>1428.20462482944</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>45.41</t>
+          <t>1649.43198151582</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>43.68</t>
+          <t>1868.92749049352</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>40.93</t>
+          <t>1817.72581885165</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.821684755536959</t>
+          <t>1471.44432951786</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.839100636076563</t>
+          <t>1592.94086142744</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.898078280441284</t>
+          <t>1286.75017844339</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.904384898541739</t>
+          <t>1391.17100301291</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.929851826238597</t>
+          <t>1595.51180627984</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.01871863654664</t>
+          <t>1707.35850283007</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.04756224641374</t>
+          <t>1918.2977352697</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.00792264839678</t>
+          <t>2032.21344297029</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.877192137997102</t>
+          <t>2305.51284265929</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.802021683764487</t>
+          <t>1871.68400243659</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.804162377075274</t>
+          <t>1901.13387769375</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.793408381912368</t>
+          <t>1838.43274371116</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.724495030641948</t>
+          <t>1970.25131295255</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.679660773115357</t>
+          <t>2191.63462181704</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.716576242819136</t>
+          <t>1917.68043335126</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>31459057.8073685</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>58333622.5361252</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>35520067.3680876</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>73801694.0372589</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>126579690.269831</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>159790500.223151</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>191478034.154755</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>235701315.525723</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>242831460.25293</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>115645474.820288</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>154087161.041906</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>193206883.539128</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>231834695.326714</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>283607582.249762</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>239134648.639499</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-39046488.4576435</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-20028320.2670244</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-44205366.9566002</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>-17699453.7695878</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>19263823.2440191</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>40431222.2542619</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>105102749.509296</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>117244188.124886</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>131357557.640602</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>-8753498.7689736</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>29855010.3744467</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>60478022.6161096</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>64662562.672569</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>80696775.4175017</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>22399185.6145576</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>70505546.265012</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>78361942.8031496</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>79725434.3246878</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>91501147.8068468</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>107315867.025812</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>119359277.968889</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>86375284.6454587</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>118457127.400837</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>111473902.612328</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>124398973.589262</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>124232150.667459</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>132728860.923019</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>167172132.654145</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>202910806.832261</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>216735463.024942</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>3601.38209159796</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>3618.34064377228</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>3513.19330316269</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>3409.81475491174</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>3451.79033116308</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>3477.08837771357</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>2946.98084859037</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>3433.16964463213</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>3494.23477780846</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>3805.96669725142</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>3803.36323861043</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>3835.17977374382</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>3876.97909423026</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>3947.58698366161</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>3977.77240675882</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3601.38209159796</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3618.34064377228</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3513.19330316269</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3409.81475491174</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3451.79033116308</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>3477.08837771357</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2946.98084859037</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3433.16964463213</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>3494.23477780846</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>3805.96669725142</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>3803.36323861043</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>3835.17977374382</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>3876.97909423025</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>3955.24890173749</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>4150.87471700563</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>345.28</t>
+          <t>2183.75432366237</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>298.11</t>
+          <t>2112.65111979316</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>384.33</t>
+          <t>2044.26726001742</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>345.67</t>
+          <t>2297.17374123947</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>283.74</t>
+          <t>2486.67624060495</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>256.12</t>
+          <t>2847.25664877912</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>163.14</t>
+          <t>2432.65066122194</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>186.92</t>
+          <t>2722.81729745513</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>215.32</t>
+          <t>3059.03083731146</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>233.49</t>
+          <t>3345.33148452363</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>213.68</t>
+          <t>3577.48983631473</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>224.31</t>
+          <t>4339.13982305009</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>200.43</t>
+          <t>5320.73796135974</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>190.42</t>
+          <t>5961.29617365826</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>217.25</t>
+          <t>4978.86495064032</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>205.2</t>
+          <t>169527083.143723</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>182.11</t>
+          <t>172720355.522382</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>243.88</t>
+          <t>151010070.395658</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>215.82</t>
+          <t>174174562.893689</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>172.77</t>
+          <t>213664182.859092</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>153.98</t>
+          <t>273992271.92687</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>89.67</t>
+          <t>218245106.970452</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>108.95</t>
+          <t>226706884.626352</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>141.49</t>
+          <t>231112115.454031</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>133.63</t>
+          <t>220711523.167825</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>130.56</t>
+          <t>211750609.645139</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>140.28</t>
+          <t>267179112.324089</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>128.74</t>
+          <t>279306992.458794</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>115.06</t>
+          <t>282691510.896963</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>141.2</t>
+          <t>216027065.225633</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>57.79</t>
+          <t>3077.55815565765</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>47.77</t>
+          <t>2989.78848671855</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>81.56</t>
+          <t>2760.72266341456</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>2924.43956971278</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>46.34</t>
+          <t>3136.08578646415</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>37.82</t>
+          <t>3538.13613509204</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>2954.38987457375</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>14.2</t>
+          <t>3079.71544903443</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>-15.84</t>
+          <t>3638.92937598667</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>28.72</t>
+          <t>4078.39464551972</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>28.46</t>
+          <t>4367.58618560208</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>31.28</t>
+          <t>5158.88821386639</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>24.55</t>
+          <t>6223.19467713802</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>7.64</t>
+          <t>6853.35799509956</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>23.05</t>
+          <t>5595.79028406079</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>500.14</t>
+          <t>458023957.805331</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>504.716</t>
+          <t>477932499.982919</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>492.003</t>
+          <t>374087773.846851</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>484.152</t>
+          <t>422734995.460179</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>496.741</t>
+          <t>528137596.986068</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>506.03</t>
+          <t>638024112.603733</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>437.682</t>
+          <t>573127275.841161</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>519.526</t>
+          <t>573989242.359084</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>526.166</t>
+          <t>645647204.726948</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>566.399</t>
+          <t>537602542.214746</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>574.002</t>
+          <t>567851239.010891</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>591.352</t>
+          <t>653011751.21351</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>616.873</t>
+          <t>699409424.108436</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>648.027</t>
+          <t>734616376.962974</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>674.378</t>
+          <t>584970083.068094</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>441.039</t>
+          <t>-893.803831995282</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>445.074</t>
+          <t>-877.137366925392</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>433.863</t>
+          <t>-716.455403397146</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>426.94</t>
+          <t>-627.265828473319</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>438.041</t>
+          <t>-649.409545859193</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>446.232</t>
+          <t>-690.879486312916</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>388.332</t>
+          <t>-521.739213351805</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>461.261</t>
+          <t>-356.898151579299</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>465.655</t>
+          <t>-579.898538675215</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>499.741</t>
+          <t>-733.063160996098</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>506.296</t>
+          <t>-790.096349287349</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>521.353</t>
+          <t>-819.748390816298</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>543.777</t>
+          <t>-902.456715778277</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>566.494</t>
+          <t>-892.061821441303</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>574.758</t>
+          <t>-616.925333420476</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>589.626</t>
+          <t>-288496874.661608</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>589.12</t>
+          <t>-305212144.460537</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>500.998</t>
+          <t>-223077703.451194</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>537.497</t>
+          <t>-248560432.56649</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>619.498</t>
+          <t>-314473414.126976</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>715.911</t>
+          <t>-364031840.676862</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>585.596</t>
+          <t>-354882168.870709</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>608.03</t>
+          <t>-347282357.732732</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>639.942</t>
+          <t>-414535089.272917</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>624.592</t>
+          <t>-316891019.046921</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>594.731</t>
+          <t>-356100629.365752</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>666.83</t>
+          <t>-385832638.889421</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>666.827</t>
+          <t>-420102431.649642</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>697.156</t>
+          <t>-451924866.066011</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>620.933</t>
+          <t>-368943017.842461</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1385.82335</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1423.35312</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1377.26698</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1476.38768</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1473.61581</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1515.93832</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>1418.21509</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1626.93416</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1868.283</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>1984.44397</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.003</t>
+          <t>2041.98878</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2193.14696</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2538.99753</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.005</t>
+          <t>2825.1127</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.004</t>
+          <t>2576.19549</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>249.185</t>
+          <t>0.0408082018147764</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>248.52</t>
+          <t>0.0376896455875792</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>241.857</t>
+          <t>0.0495962516759357</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>237.705</t>
+          <t>0.0447526145337143</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>242.081</t>
+          <t>0.0405197614288493</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>246.374</t>
+          <t>0.0421049528694169</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>214.902</t>
+          <t>0.0469073191731178</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>252.273</t>
+          <t>0.0580598351060868</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>246.31</t>
+          <t>0.0485127775549195</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>264.975</t>
+          <t>0.0429817634714068</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>259.24</t>
+          <t>0.0518902133423115</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>262.318</t>
+          <t>0.0427299673264274</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>260.746</t>
+          <t>0.051520688176504</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>258.964</t>
+          <t>0.0377331288637923</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>264.752</t>
+          <t>0.0303310725219007</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1616.02247943738</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1715.50960720146</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1667.34448396809</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1754.22786698853</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1785.88735535493</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1708.42222994882</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1795.89572328168</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>1963.83622744647</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2341.0084328578</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2657.18545419359</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2726.00838892361</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>2910.50556607688</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3330.69237946551</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>4211.27127438239</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>0.002</t>
+          <t>3969.63156938789</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>180.199</t>
+          <t>1838.78028224347</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>195.94</t>
+          <t>1951.70874750034</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>158.908</t>
+          <t>1896.64032042978</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>174.187</t>
+          <t>1995.10864087904</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>202.475</t>
+          <t>2031.06693944933</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>219.114</t>
+          <t>1942.8079854763</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>252.78</t>
+          <t>2027.75751254768</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>273.037</t>
+          <t>2217.01603428793</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>307.241</t>
+          <t>2649.87773934298</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>245.761</t>
+          <t>3024.69870145227</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>253.075</t>
+          <t>3105.22631611993</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>249.916</t>
+          <t>3318.28575340782</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>276.343</t>
+          <t>3798.83718075924</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>314.508</t>
+          <t>4801.04665285912</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>277.091</t>
+          <t>4526.25911690874</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>144.75</t>
+          <t>10387.5856369219</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>127.15</t>
+          <t>10472.6167481845</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>173.03</t>
+          <t>9483.38162869941</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>145.1</t>
+          <t>10201.0690177384</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>116.34</t>
+          <t>10220.2398503971</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>103.65</t>
+          <t>10254.1775437209</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>53.62</t>
+          <t>10625.9934267763</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>68.94</t>
+          <t>11585.0704704321</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>51.56</t>
+          <t>13726.6270515646</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>103.34</t>
+          <t>15507.6288577581</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>100.06</t>
+          <t>15925.640501504</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>108.61</t>
+          <t>17769.8778930057</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>96.78</t>
+          <t>21012.7662506392</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>80.12</t>
+          <t>24984.4029645788</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>107.43</t>
+          <t>24997.3651176415</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>3.407</t>
+          <t>1838.78028224347</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>3.348</t>
+          <t>1971.81963499446</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>2.996</t>
+          <t>2014.16080919266</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2.967</t>
+          <t>2105.0491934226</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>3.278</t>
+          <t>2187.32487864978</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>3.52</t>
+          <t>2220.06132249716</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>3.158</t>
+          <t>2341.96233993632</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>3.071</t>
+          <t>2416.85037926708</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>2.717</t>
+          <t>2406.06824787509</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>2.459</t>
+          <t>2461.64909418327</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>2.161</t>
+          <t>2512.31847011829</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>2.418</t>
+          <t>2574.27894368699</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>2.018</t>
+          <t>2626.41985086363</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>1.864</t>
+          <t>3048.45170473549</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>1.966</t>
+          <t>2961.89450481308</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1616.02247943738</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>1733.12184215755</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1770.48890676647</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>1850.65172602171</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1922.98613329567</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>1951.74472640863</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>2073.73783740309</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>2140.18170002683</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>2124.94077630928</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>2160.56270123431</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>2203.17336956751</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2255.01404420631</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>2299.23424464493</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>2670.20692419726</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>2593.97155767355</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1358.93245775653</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>1357.14530249966</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1348.45227957022</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>1444.88629912096</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1442.58140055067</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>1511.2096245237</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>1361.36418745232</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1530.27083571207</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>1758.04608065702</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>1859.37692854773</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>2062.21746388007</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2187.51092659218</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>2732.02415924076</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>2811.66718714088</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>2575.92271309126</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>441038708.5766</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>445074055.750719</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>433862869.081594</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>426939703.638402</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>438041476.220208</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>446232385.027447</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>388332410.868854</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>461261338.430849</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>465655035.103148</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>499741448.784071</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>506295592.27042</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>521353496.345582</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>543776767.204529</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>566493582.379361</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>574758407.740725</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>500139945.279738</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>504716047.729708</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>492002509.942257</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>484151608.15385</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>496741069.857772</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>506029598.512922</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>437681764.141144</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>519525928.548431</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>526165846.23679</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>566398748.282775</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>574002283.658738</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>591351801.430865</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>616873359.666589</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>648027223.101024</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>674377514.142872</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>249184854.029122</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>248519519.971902</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>241856774.998349</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>237705284.919047</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>242080884.916954</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>246373744.267785</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>214902348.644951</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>252272807.837386</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>246309543.213824</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>264975153.276005</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>259240050.839006</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>262317634.354752</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>260746495.728625</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>258964094.34228</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>264751853.916203</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>138874.446687167</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>139488.262001645</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>140044.246782362</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>141987.657087953</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>143908.239551269</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>145532.567350409</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>148518.699858705</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>151325.446256559</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>150581.137128626</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>148818.629624851</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>150919.65916683</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>154191.416391832</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>159111.861238722</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>163839.80861896</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>162466.36194054</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>122463.736798588</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>123005.017926314</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>123495.302319692</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>125209.060997641</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>126902.689385716</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>128335.071345203</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>131772.967257186</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>134354.368171712</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>133263.808734455</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>131304.73504799</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>133117.864507571</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>135939.780428245</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>140257.853856829</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>143503.761848436</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>144492.532243455</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>272137948.345955</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>273340778.991406</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>274430285.096707</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>278238586.090692</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>282002153.713565</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>285185181.586899</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>244531553.853267</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>288899268.348295</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>277160855.202434</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>284000169.133413</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>286041214.56216</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>287986878.933645</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>300122877.824299</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>306882575.853023</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>307779660.295915</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>239979570.570101</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>241040263.441192</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>242001023.264924</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>245359299.619592</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>248678128.718725</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>251485020.101561</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>216960210.868469</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>256499350.402692</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>245286440.92271</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>250577276.888324</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>252301097.510267</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>253897875.799843</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>264559728.038222</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>271436883.391728</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>264648734.990132</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.153249373821671</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.151591592079525</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.141357934736138</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.131085475404161</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.13503866866876</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.137628540907754</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.134641513454121</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.138774875738712</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.123858063604186</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.171829178515103</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.181345393421768</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.184575841473869</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.19112187778463</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.207927195251845</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.211989600542139</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.169808085044118</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.176824940679784</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.168692369777653</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.160217209274112</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.174665667557867</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.179910216418803</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.187035676667841</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.18621192661329</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.133184295915879</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.195344038586568</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.197423507628787</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.207830894374601</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.199025936164546</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.197474450575818</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.216775569682832</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.676942541134211</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.671583467240692</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.689949695486209</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.708697315321728</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.690295663773374</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.682461242673443</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.678322809878038</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.675013197647998</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.742957640479934</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.632826782898329</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.621231098949445</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.607593264151529</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.609852186050824</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.594598354172337</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.57123482977503</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.233175632421713</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.23253959469975</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.220194395322882</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.20815449878133</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.211434792120948</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.215353752477266</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.21580284304186</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.223774869612283</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.261459806563282</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.266378193511664</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.279458030492262</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.286412987163339</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.298013364501723</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.318452698794842</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.329335976037564</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.223112108065907</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.23076560909183</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.222322563509499</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.213259917236434</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.230516427377225</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.236222063272243</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.243682664860547</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.24066817692975</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.235794531713251</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.246454552404253</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.246466736759821</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.255423644330556</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.247899377409721</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.244786230180686</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.261406427925119</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.54371225951238</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.536694796208419</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.557483041167619</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.578585583982235</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.558048780501827</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.548424184250491</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.540514492097593</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.535556953457967</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.502745661723467</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.487167254084083</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.474075232747917</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.458163368506105</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.454087258088556</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.436761071024472</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.409257596037317</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>6810.28788</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>6759.79225</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>6504.52899</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>7022.21424</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>7201.39947</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>7612.00423</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>7085.95531</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>7660.96435</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>9137.04683</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>10679.72391</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>11410.39724</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>12906.4076</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>15298.69514</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>17266.45712</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>16001.56341</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3197.71274</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>3308.85405</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>3245.0926</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>3439.99494</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>3473.64834</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>3454.01761</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>3389.1217</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>3747.28687</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>4407.92382</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>4884.07563</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>5167.44378</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>5505.79668</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>6530.86134</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>7612.71384</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>7102.18183</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>8540.10449177539</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>8906.54079634492</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>9298.47153182451</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>9715.44255502075</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>10129.7218552802</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>10575.0429322389</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10878.9484176219</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>11000.1283463253</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>11266.8232314971</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>11529.1787391199</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>11932.1325426299</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>12320.7451710381</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>12719.6954845692</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>12822.9626287163</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>12793.4869850017</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
